--- a/examples/05_comprehensive_line/01_Infrastructure.xlsx
+++ b/examples/05_comprehensive_line/01_Infrastructure.xlsx
@@ -1433,7 +1433,7 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>REVERSE</t>
+          <t>NOMINAL</t>
         </is>
       </c>
     </row>
